--- a/progress/Defect_Tracker Template_v0.1.xlsx
+++ b/progress/Defect_Tracker Template_v0.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ganesh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ganesh\ai-security-analysis-agent\progress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E183FD4-BCFE-44F8-BA10-CF9DBD591620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4B553B-3BA9-4980-8658-07B1EA343DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Defects" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="42">
   <si>
     <t>Sl No</t>
   </si>
@@ -93,28 +93,73 @@
     <t>Streamlit frontend has a very basic two-column layout without custom styling, status badges, or clean spacing.</t>
   </si>
   <si>
-    <t>Added basic split-screen columns for Milestone 1; full UI polish and dashboard tabs scheduled for Sprint 2.</t>
-  </si>
-  <si>
     <t>Open</t>
   </si>
   <si>
-    <t>Basic UI works for Milestone 1 demo; will be refined in Sprint 2.</t>
-  </si>
-  <si>
     <t>Frontend directly imports Python functions instead of communicating through a decoupled FastAPI backend.</t>
   </si>
   <si>
-    <t>Kept direct module calls for Milestone 1 prototype; FastAPI REST endpoints will be integrated in Sprint 2.</t>
-  </si>
-  <si>
     <t>Automated unit test scripts inside the tests/ folder have not been written yet for the parser and RAG modules.</t>
   </si>
   <si>
-    <t>Performed manual unit testing for Demo.</t>
-  </si>
-  <si>
-    <t>Manual test cases passed for Milestone 1.</t>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Upgraded ui/app.py with 5-tier Severity Pyramid metrics, 4 Complexity cards, Quality Assessment scores, and 5 report tabs.</t>
+  </si>
+  <si>
+    <t>Built FastAPI backend (services/api.py) with /api/v1/analyze and /api/v1/history endpoints plus SQLite persistence</t>
+  </si>
+  <si>
+    <t>Added tests/test_agents.py to automatically validate parallel agent accuracy on Python and Java sample files.</t>
+  </si>
+  <si>
+    <t>Resolved in Sprint 2; dashboard now renders all 6 security report fields and quality metrics.</t>
+  </si>
+  <si>
+    <t>Resolved in Sprint 2; Streamlit now communicates with FastAPI on port 8000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolved in Sprint 2; automated validation suite passes for both Python and Java samples.   </t>
+  </si>
+  <si>
+    <t>Parallel agents caused a 120s ReadTimeoutError because rag/retriever.py re-computed embeddings on CPU via FAISS.from_documents() on every call.</t>
+  </si>
+  <si>
+    <t>Uvicorn reloader threw sqlite3.OperationalError: unable to open database file on Windows when initializing data/reviews.db</t>
+  </si>
+  <si>
+    <t>Streamlit file watcher raised ModuleNotFoundError: No module named 'torchvision' when inspecting transformers modules.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interactive RAG Conversational Code Assistant, PR Summary Agent, and downloadable report export buttons are not yet integrated into the UI.   </t>
+  </si>
+  <si>
+    <t>Sprint 2</t>
+  </si>
+  <si>
+    <t>Cached the HuggingFaceEmbeddings instance in rag/embeddings.py and switched rag/retriever.py to FAISS.from_embeddings() using stored ChromaDB vectors.</t>
+  </si>
+  <si>
+    <t>Anchored DB_PATH in services/database.py to the absolute project root (ROOT_DIR / "data" / "reviews.db") and auto-created the data/ folder.</t>
+  </si>
+  <si>
+    <t>Created .streamlit/config.toml (fileWatcherType = "none") and moved fallback src.workflow import inside the execution block in ui/app.py.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scoped out of Milestone 2 per project roadmap; scheduled for implementation in Milestone 3 (Sprint 3).   </t>
+  </si>
+  <si>
+    <t>Retrieval latency reduced from &gt;120s to &lt;0.05s during parallel LangGraph execution.</t>
+  </si>
+  <si>
+    <t>SQLite database initializes and saves review history reliably across Uvicorn workers.</t>
+  </si>
+  <si>
+    <t>Eliminated watcher tracebacks and improved Streamlit startup speed.</t>
+  </si>
+  <si>
+    <t>Tracked for Sprint 3 (Milestone 3) delivery.</t>
   </si>
 </sst>
 </file>
@@ -603,7 +648,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -626,16 +671,16 @@
         <v>10</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I2" s="8">
-        <v>46307</v>
+        <v>46321</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K2" s="9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="93.6" x14ac:dyDescent="0.3">
@@ -649,7 +694,7 @@
         <v>46306</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>16</v>
@@ -661,19 +706,19 @@
         <v>9</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I3" s="8">
-        <v>46307</v>
+        <v>46321</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -684,7 +729,7 @@
         <v>46308</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>16</v>
@@ -699,71 +744,159 @@
         <v>25</v>
       </c>
       <c r="I4" s="8">
-        <v>46309</v>
+        <v>46323</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="140.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="8">
+        <v>46319</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="8">
+        <v>46322</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="8">
+        <v>46321</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="8">
+        <v>46322</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="124.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="8">
+        <v>46322</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="8">
+        <v>46322</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="109.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="8">
+        <v>46323</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="8">
+        <v>46324</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
+      <c r="C9" s="8"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="6"/>
@@ -1105,18 +1238,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1138,18 +1271,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B149665-BEBB-4C97-BAA6-72374EAA67F9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>